--- a/data.mn/public/datasets/cpi-food-ulaanbaatar.xlsx
+++ b/data.mn/public/datasets/cpi-food-ulaanbaatar.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1035,4 +1036,634 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>сар</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>утга</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2020-02</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2020-03</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2020-04</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2020-05</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2020-06</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2020-07</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2020-08</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-4.6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2020-09</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-2.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2020-10</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2020-11</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2021-01</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2021-02</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2021-05</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>-2.9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2021-09</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2022-01</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2022-03</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>-4.8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>-4.1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>-2.3</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data.mn/public/datasets/cpi-food-ulaanbaatar.xlsx
+++ b/data.mn/public/datasets/cpi-food-ulaanbaatar.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -123,6 +123,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>data.mn</author>
+  </authors>
+  <commentList>
+    <comment ref="A62" authorId="0" shapeId="0">
+      <text>
+        <t>Basis change: 2020=100 → 2023=100</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>data.mn</author>
+  </authors>
+  <commentList>
+    <comment ref="A62" authorId="0" shapeId="0">
+      <text>
+        <t>Суурь өөрчлөгдсөн: 2020=100 → 2023=100</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -414,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B61"/>
+  <dimension ref="A1:B79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1033,8 +1063,189 @@
         <v>1.9</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1044,7 +1255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B61"/>
+  <dimension ref="A1:B79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1663,7 +1874,188 @@
         <v>1.9</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/data.mn/public/datasets/cpi-food-ulaanbaatar.xlsx
+++ b/data.mn/public/datasets/cpi-food-ulaanbaatar.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="English" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B79"/>
+  <dimension ref="A1:B81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1241,6 +1241,26 @@
       </c>
       <c r="B79" t="n">
         <v>0.3</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>-2.9</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>-1.4</v>
       </c>
     </row>
   </sheetData>
@@ -1255,7 +1275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B79"/>
+  <dimension ref="A1:B81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2054,6 +2074,26 @@
         <v>0.3</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>-2.9</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>-1.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
